--- a/docs/design/roguelike_cards.xlsx
+++ b/docs/design/roguelike_cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99be967cde7e20d9/문서/GitHub/Project_adventureOfGengar/docs/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6A8E2E61C581AC075E46E2F021523071AEF1B893" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3C8E05C7C481AC275956DA9221D2BA60F7669127" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="30" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개요" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="607">
   <si>
     <t>로그라이크 카드 시스템 기획 (초안)</t>
   </si>
@@ -428,7 +428,7 @@
     <t>하</t>
   </si>
   <si>
-    <t>기존 공격력 업그레이드(최대 4)를 5로</t>
+    <t>기존 공격력 업그레이드(최대 4)를 5로. 밸런스: 너무 안 나와서 일반 -&gt; 희귀, 같은 등급 안에서 뽑힐 비중 4배 (한 칸 확률 약 2.8% -&gt; 6.7%)</t>
   </si>
   <si>
     <t>A02</t>
@@ -671,15 +671,18 @@
     <t>CURSE</t>
   </si>
   <si>
-    <t>맞은 적이 3초 동안 받는 모든 피해 증가 (보라 표식)</t>
-  </si>
-  <si>
-    <t>받는 피해 +25%</t>
+    <t>맞은 적이 2초 동안 받는 피해 2배 (보라 표식). 같은 적은 15초 동안 다시 걸리지 않음</t>
+  </si>
+  <si>
+    <t>2초간 피해 2배 / 쿨 15초</t>
   </si>
   <si>
     <t>보라 눈</t>
   </si>
   <si>
+    <t>밸런스: +25% 는 기본 피해 1에서 반올림되어 효과가 없었음 -&gt; 2초간 2배. 보스에게 2배가 계속 이어지지 않도록 대상별 15초 쿨타임</t>
+  </si>
+  <si>
     <t>A14</t>
   </si>
   <si>
@@ -1472,6 +1475,9 @@
     <t>폭발·분열 조각에 맞은 적에게도 저주 표식</t>
   </si>
   <si>
+    <t>같은 적은 15초 쿨타임 (보스 포함)</t>
+  </si>
+  <si>
     <t>치명타 + 모든 피해</t>
   </si>
   <si>
@@ -1523,7 +1529,7 @@
     <t>처형자 + 저주탄</t>
   </si>
   <si>
-    <t>곱연산: 저주 걸린 빈사 적에게 x1.5 x1.25</t>
+    <t>곱연산: 저주 걸린 빈사 적에게 x1.5 x2</t>
   </si>
   <si>
     <t>최후의 저항 + 그림자 보호막</t>
@@ -2738,11 +2744,11 @@
       </c>
       <c r="B4" s="10">
         <f>COUNTIFS('카드 목록'!$E:$E,$A4,'카드 목록'!$D:$D,"일반")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="10">
         <f>COUNTIFS('카드 목록'!$E:$E,$A4,'카드 목록'!$D:$D,"희귀")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="10">
         <f>COUNTIFS('카드 목록'!$E:$E,$A4,'카드 목록'!$D:$D,"영웅")</f>
@@ -2888,11 +2894,11 @@
       </c>
       <c r="B10" s="11">
         <f>SUM(B4:B9)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(C4:C9)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D4:D9)</f>
@@ -3256,7 +3262,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>89</v>
       </c>
@@ -3267,7 +3273,7 @@
         <v>91</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>34</v>
@@ -3752,7 +3758,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>176</v>
       </c>
@@ -3790,17 +3796,19 @@
       <c r="M14" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>32</v>
@@ -3812,37 +3820,37 @@
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I15" s="27">
         <v>1</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>138</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>32</v>
@@ -3854,17 +3862,17 @@
         <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" s="27">
         <v>1</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>111</v>
@@ -3873,18 +3881,18 @@
         <v>138</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>32</v>
@@ -3896,37 +3904,37 @@
         <v>39</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I17" s="27">
         <v>1</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>111</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>29</v>
@@ -3938,17 +3946,17 @@
         <v>92</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I18" s="27">
         <v>4</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>96</v>
@@ -3960,13 +3968,13 @@
     </row>
     <row r="19" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>29</v>
@@ -3975,22 +3983,22 @@
         <v>35</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I19" s="27">
         <v>99</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>111</v>
@@ -3999,18 +4007,18 @@
         <v>97</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>30</v>
@@ -4022,17 +4030,17 @@
         <v>92</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I20" s="27">
         <v>2</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>111</v>
@@ -4044,13 +4052,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>30</v>
@@ -4062,17 +4070,17 @@
         <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I21" s="27">
         <v>1</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>111</v>
@@ -4084,13 +4092,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>30</v>
@@ -4102,17 +4110,17 @@
         <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I22" s="27">
         <v>1</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>111</v>
@@ -4124,13 +4132,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>31</v>
@@ -4142,17 +4150,17 @@
         <v>39</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I23" s="27">
         <v>1</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>111</v>
@@ -4164,13 +4172,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>31</v>
@@ -4182,17 +4190,17 @@
         <v>134</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I24" s="27">
         <v>3</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>96</v>
@@ -4204,13 +4212,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>29</v>
@@ -4222,17 +4230,17 @@
         <v>92</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I25" s="27">
         <v>3</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>96</v>
@@ -4244,13 +4252,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>29</v>
@@ -4262,17 +4270,17 @@
         <v>92</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I26" s="27">
         <v>2</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>111</v>
@@ -4281,18 +4289,18 @@
         <v>97</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>30</v>
@@ -4304,17 +4312,17 @@
         <v>134</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I27" s="27">
         <v>2</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>96</v>
@@ -4323,18 +4331,18 @@
         <v>97</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>30</v>
@@ -4346,17 +4354,17 @@
         <v>39</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I28" s="27">
         <v>1</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>111</v>
@@ -4365,18 +4373,18 @@
         <v>138</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>29</v>
@@ -4388,20 +4396,20 @@
         <v>92</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I29" s="27">
         <v>2</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>97</v>
@@ -4410,13 +4418,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>29</v>
@@ -4428,17 +4436,17 @@
         <v>92</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I30" s="27">
         <v>2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>111</v>
@@ -4447,18 +4455,18 @@
         <v>97</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>30</v>
@@ -4470,37 +4478,37 @@
         <v>134</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I31" s="27">
         <v>2</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>138</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>30</v>
@@ -4512,17 +4520,17 @@
         <v>39</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I32" s="27">
         <v>1</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>111</v>
@@ -4531,18 +4539,18 @@
         <v>97</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>31</v>
@@ -4554,37 +4562,37 @@
         <v>39</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I33" s="27">
         <v>1</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>97</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>31</v>
@@ -4596,17 +4604,17 @@
         <v>39</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I34" s="27">
         <v>1</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>111</v>
@@ -4615,18 +4623,18 @@
         <v>138</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>32</v>
@@ -4638,17 +4646,17 @@
         <v>39</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I35" s="27">
         <v>1</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>111</v>
@@ -4657,18 +4665,18 @@
         <v>138</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>29</v>
@@ -4680,17 +4688,17 @@
         <v>92</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I36" s="27">
         <v>3</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>96</v>
@@ -4699,18 +4707,18 @@
         <v>97</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>30</v>
@@ -4722,17 +4730,17 @@
         <v>92</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I37" s="27">
         <v>3</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>96</v>
@@ -4744,13 +4752,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>29</v>
@@ -4762,17 +4770,17 @@
         <v>39</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I38" s="27">
         <v>1</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>111</v>
@@ -4784,13 +4792,13 @@
     </row>
     <row r="39" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>30</v>
@@ -4802,39 +4810,39 @@
         <v>39</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I39" s="27">
         <v>1</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M39" s="10" t="s">
         <v>138</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>31</v>
@@ -4846,39 +4854,39 @@
         <v>39</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I40" s="27">
         <v>1</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>32</v>
@@ -4890,39 +4898,39 @@
         <v>39</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I41" s="27">
         <v>1</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>29</v>
@@ -4934,17 +4942,17 @@
         <v>92</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I42" s="27">
         <v>2</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>111</v>
@@ -4956,13 +4964,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>29</v>
@@ -4974,17 +4982,17 @@
         <v>92</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I43" s="27">
         <v>3</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>111</v>
@@ -4996,13 +5004,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>29</v>
@@ -5014,17 +5022,17 @@
         <v>39</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I44" s="27">
         <v>1</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>111</v>
@@ -5036,13 +5044,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>30</v>
@@ -5054,17 +5062,17 @@
         <v>92</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I45" s="27">
         <v>2</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>111</v>
@@ -5073,18 +5081,18 @@
         <v>97</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>30</v>
@@ -5096,17 +5104,17 @@
         <v>92</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I46" s="27">
         <v>3</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>111</v>
@@ -5118,13 +5126,13 @@
     </row>
     <row r="47" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>31</v>
@@ -5136,17 +5144,17 @@
         <v>134</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I47" s="27">
         <v>2</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>111</v>
@@ -5155,18 +5163,18 @@
         <v>138</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>31</v>
@@ -5178,17 +5186,17 @@
         <v>39</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I48" s="27">
         <v>1</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>111</v>
@@ -5200,13 +5208,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>31</v>
@@ -5218,17 +5226,17 @@
         <v>39</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I49" s="27">
         <v>1</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>111</v>
@@ -5240,13 +5248,13 @@
     </row>
     <row r="50" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>32</v>
@@ -5258,26 +5266,26 @@
         <v>39</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I50" s="27">
         <v>1</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>111</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5342,7 +5350,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -5350,10 +5358,10 @@
         <v>80</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
@@ -5361,10 +5369,10 @@
         <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
@@ -5372,10 +5380,10 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
@@ -5383,191 +5391,191 @@
         <v>134</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5594,7 +5602,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -5608,39 +5616,39 @@
         <v>78</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F4" s="27">
         <v>6</v>
@@ -5652,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -5660,16 +5668,16 @@
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F5" s="27">
         <v>3</v>
@@ -5681,7 +5689,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -5689,16 +5697,16 @@
         <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F6" s="27">
         <v>1.5</v>
@@ -5710,7 +5718,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.3">
@@ -5718,16 +5726,16 @@
         <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F7" s="27">
         <v>8</v>
@@ -5739,17 +5747,17 @@
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -5757,13 +5765,13 @@
         <v>38</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -5836,7 +5844,7 @@
     </row>
     <row r="15" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
@@ -5870,35 +5878,35 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B4" s="27">
         <v>2</v>
@@ -5918,7 +5926,7 @@
         <v>24</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I4" s="33">
         <v>6</v>
@@ -5926,7 +5934,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B5" s="27">
         <v>2</v>
@@ -5946,7 +5954,7 @@
         <v>14</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I5" s="33">
         <v>3</v>
@@ -5954,7 +5962,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B6" s="27">
         <v>4</v>
@@ -5974,18 +5982,18 @@
         <v>24</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I6" s="34">
         <v>0.85</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B7" s="27">
         <v>4</v>
@@ -6029,16 +6037,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -6054,7 +6062,7 @@
         <v>6</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I10" s="35">
         <f>E8*I6</f>
@@ -6074,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I11" s="35">
         <f>IFERROR(MATCH(I10,$C$10:$C$24,1),0)+1</f>
@@ -6094,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I12" s="35">
         <f>(E8+F8)*I6</f>
@@ -6114,7 +6122,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I13" s="35">
         <f>IFERROR(MATCH(I12,$C$10:$C$24,1),0)+1</f>
@@ -6134,7 +6142,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I14" s="35">
         <f>I13-1</f>
@@ -6154,7 +6162,7 @@
         <v>81</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I15" s="35">
         <v>2</v>
@@ -6173,7 +6181,7 @@
         <v>105</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I16" s="35">
         <f>I14+I15</f>
@@ -6206,7 +6214,7 @@
         <v>162</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
@@ -6323,23 +6331,23 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B3" s="33">
         <v>50</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="32" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B4" s="33">
         <v>0</v>
@@ -6347,33 +6355,33 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -6390,7 +6398,7 @@
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F8" s="27">
         <v>61</v>
@@ -6418,7 +6426,7 @@
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F9" s="10">
         <f>H8+68</f>
@@ -6487,15 +6495,15 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
@@ -6506,10 +6514,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -6520,10 +6528,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -6534,10 +6542,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -6548,10 +6556,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -6562,10 +6570,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
@@ -6604,27 +6612,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>78</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -6632,19 +6640,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -6652,16 +6660,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>89</v>
@@ -6672,16 +6680,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>99</v>
@@ -6692,19 +6700,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -6712,19 +6720,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -6732,19 +6740,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -6752,19 +6760,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6775,16 +6783,16 @@
         <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -6792,19 +6800,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -6815,16 +6823,16 @@
         <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -6835,16 +6843,16 @@
         <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -6852,24 +6860,24 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/docs/design/roguelike_cards.xlsx
+++ b/docs/design/roguelike_cards.xlsx
@@ -2783,7 +2783,7 @@
       </c>
       <c r="N2" s="38" t="inlineStr">
         <is>
-          <t>기존 공격력 업그레이드(최대 4)를 5로. 밸런스: 너무 안 나와서 일반 -&gt; 희귀, 같은 등급 안에서 뽑힐 비중 4배 (한 칸 확률 약 2.8% -&gt; 6.7%)</t>
+          <t>기존 공격력 업그레이드(최대 4)를 5로. 밸런스: 너무 안 나와서 일반 -&gt; 희귀, 비중 4배. 0.3.1: 비중 4일 때 레벨업 화면 한 번에 나올 확률이 약 20%(희귀 칸의 4/19)라 너무 자주 보여서 비중 2로 (약 11%)</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="G34" s="38" t="inlineStr">
         <is>
-          <t>대시로 통과한 적에게 피해 (공격력 x2)</t>
+          <t>대시로 통과한 적에게 피해 (공격력 x2). 대시 중 몸 앞에 초승달 칼날이 펼쳐지고, 그만큼 앞쪽 22px 도 벤다</t>
         </is>
       </c>
       <c r="H34" s="26" t="inlineStr">
@@ -4836,7 +4836,7 @@
       <c r="J34" s="38" t="n"/>
       <c r="K34" s="38" t="inlineStr">
         <is>
-          <t>칼날 잔상</t>
+          <t>초승달 칼날</t>
         </is>
       </c>
       <c r="L34" s="38" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>
-          <t>무적 대시와 시너지 (선행 조건은 두지 않음)</t>
+          <t>무적 대시와 시너지 (선행 조건은 두지 않음). 0.3.1: 칼날 연출 + 앞쪽 판정 추가</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="N47" s="38" t="inlineStr">
         <is>
-          <t>0.3.0: 누구나 코인으로 다시 뽑을 수 있게 되어(15코인부터 +10, '상점' 시트) 이 카드는 무료 횟수가 됨. 레벨업 화면 ↑ 키</t>
+          <t>0.3.0: 누구나 코인으로 다시 뽑을 수 있게 되어(15코인부터 +10, '상점' 시트) 이 카드는 무료 횟수가 됨. 0.3.1: 다시 뽑기 키를 ↑ 에서 R 로</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G49" s="38" t="inlineStr">
         <is>
-          <t>레벨업 때 카드가 4장 나옴</t>
+          <t>레벨업·보스 보너스·상점 뽑기에서 카드가 4장 나옴</t>
         </is>
       </c>
       <c r="H49" s="26" t="inlineStr">
@@ -5823,7 +5823,11 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N49" s="38" t="n"/>
+      <c r="N49" s="38" t="inlineStr">
+        <is>
+          <t>0.3.1: 상점 뽑기에 적용되지 않던 버그 수정</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27" customHeight="1" s="37">
       <c r="A50" s="10" t="inlineStr">
@@ -5887,7 +5891,7 @@
       </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
-          <t>도트 스프라이트 1종 추가 필요</t>
+          <t>도트 스프라이트 1종 추가 필요. 0.3.1: 스테이지 중에 얻으면 다음 스테이지가 아니라 바로 나오도록 수정</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="37" min="1" max="1"/>
@@ -7564,7 +7568,7 @@
       </c>
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>리롤 카드의 무료 횟수가 남아 있으면 먼저 쓰고, 없으면 코인을 냄. 코인이 모자라면 ↑ 안내에 필요한 코인을 붉게 표시</t>
+          <t>리롤 카드의 무료 횟수가 남아 있으면 먼저 쓰고, 없으면 코인을 냄. R 키 (0.3.1, 이전에는 ↑). 코인이 모자라면 안내에 필요한 코인을 붉게 표시</t>
         </is>
       </c>
       <c r="C27" s="41" t="n"/>
@@ -7592,14 +7596,97 @@
       <c r="G28" s="41" t="n"/>
       <c r="H28" s="42" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>상점 화면 정리 (0.3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>고른 칸</t>
+        </is>
+      </c>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>금색 테두리가 깜빡이고 왼쪽에 화살표. 출발 칸은 초록(보스 전에는 분홍)으로 바뀌고 &gt;&gt;&gt; 가 흐른다</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="n"/>
+      <c r="D31" s="41" t="n"/>
+      <c r="E31" s="41" t="n"/>
+      <c r="F31" s="41" t="n"/>
+      <c r="G31" s="41" t="n"/>
+      <c r="H31" s="42" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>출발 칸</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>'NEXT STAGE' + 다음 스테이지 이름. 누르면 화면이 검게 닫히고 넘어간다</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="41" t="n"/>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="41" t="n"/>
+      <c r="G32" s="41" t="n"/>
+      <c r="H32" s="42" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>능력치 패널</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>이름을 밝게, 줄마다 옅은 띠. 카드로 올린 능력치는 초록 값으로 표시 (일시정지 화면 패널도 같다)</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="41" t="n"/>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="41" t="n"/>
+      <c r="G33" s="41" t="n"/>
+      <c r="H33" s="42" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>스테이지 클리어 화면</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
+          <t>기록이 다 나온 뒤 Z 를 눌러야 상점으로 넘어간다 (예전에는 약 3초 뒤 자동)</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="n"/>
+      <c r="D34" s="41" t="n"/>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="41" t="n"/>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="42" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>

--- a/docs/design/roguelike_cards.xlsx
+++ b/docs/design/roguelike_cards.xlsx
@@ -15,10 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경험치" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상점" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="캐릭터 패널" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보스 패턴" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스테이지 구성" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보스 패턴" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'카드 목록'!$A$1:$N$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'카드 목록'!$A$1:$N$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -816,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" style="37" min="1" max="1"/>
@@ -986,12 +987,465 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="46" customHeight="1" s="37">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>능력치 창 (0.4.0)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>플레이 중 Tab 을 누르면 게임이 멈추고 능력치 창이 열린다. 왼쪽은 캐릭터 패널, 오른쪽은 얻은 카드 격자(능력치 카드 포함). 카드에 마우스를 올리거나 방향키로 고르면 아래에 등급·분류·단계와 수치가 들어간 자세한 설명이 나온다. Tab 이나 Esc 로 닫는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1" s="37">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>스테이지 1·2 개편 (0.4.0)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>매복 결투장, 점프 버섯, 정예 적, 보물상자를 넣어 단조롭던 구간을 나눈다. 자세한 배치는 '스테이지 구성' 시트.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1" s="37">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>0.4.1 변경</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>섀도우볼이 공격력 단계마다 바로 커지게 (그림 크기 = 반지름 x 2.3). 보스 체력 900. 보스 소환 박쥐는 플레이어를 향해 천천히 날아온다. 새 적 그림자 두꺼비, 정예 특별 스킬, 결투장 제한 시간·증원·붉은 경고 ('스테이지 구성' 시트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" s="37">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>0.4.2 변경</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>피해를 10 단위로 (플레이어 기본 10, 공격력 +3/단계, 적 체력: 슬라임·마법사·두꺼비 20, 늑대 30, 박쥐 10, 스테이지마다 +10, 보스 3000). 새 카드 10종(혈사포, 레이저, 부메랑, 웨이브, 산탄, 무거운 공, 독, 냉기, 연쇄 번개, 그림자 궤도)과 등급 조정(유도·차지샷 전설-&gt;영웅, 튕김·저주 영웅-&gt;희귀). 카드로 겉모습이 바뀜(혈사포 뿔, 공중 점프 날개, 궤도 구슬). 분신은 내 사격과 같은 발 수, 차지샷도 멀티샷 수만큼, 두꺼비는 절벽을 피함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1" s="37">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>0.4.3 변경</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>기본 필살기 너프(35+3/단계, 보스 120). 보스 외 적 체력 +6 (슬라임·마법사·두꺼비 26, 늑대 36, 박쥐 16, 작은 슬라임 16). 대시 칸 카드가 공중 대시 횟수도 늘림. 분신 최대 3마리(한 줄로 따라옴). 상점 뽑기 가격 +25씩, 카드 강화 칸 추가. 영웅·전설 확률 크게 낮춤.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>0.4.4 변경</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>전설 확률 3 / 5 / 8% (일반을 그만큼 낮춤). 상점 뽑기 가격은 100코인에서 더 오르지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>0.4.5 변경</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>웨이브 공이 바닥에 바로 닿아 사라지던 문제 수정. 등급 확률을 스테이지 1 일반 50% 기준으로 재조정. 상점 강화 화면을 목록형으로 다시 만듦.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>0.4.6 변경</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>그림자 분신은 0.8초마다 플레이어와 같은 공격을 쏜다(내 사격을 따라 하지 않음). 상점 뽑기 가격은 상한 없이 그 판에서 뽑을 때마다 +25, 다음 상점에도 이어진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>0.4.7 변경</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>사거리 계산을 한 곳으로(산탄 55%는 판 내내 유지, 능력치 패널 RANGE 가 실제 값). AIR JUMP 를 DOUBLE JUMP 로 이름 변경. 전설 이동 카드 그림자 날개(비행) 추가.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="37" min="1" max="1"/>
+    <col width="22" customWidth="1" style="37" min="2" max="2"/>
+    <col width="90" customWidth="1" style="37" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>스테이지 1·2 구성 (0.4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>열 = 타일 x (1칸 32px), 바닥 윗면 = 15행. 배치 코드는 Source/Private/world/StageBuilder.cpp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>요소</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>동작</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>보상 / 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>매복 결투장</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>들어오면 양 끝 열에 마법 벽이 생기고 카메라가 결투장 화면에 묶인다. 다음 웨이브 자리에 0.8~1초 동안 소환 마법진(정예는 금빛)이 돌고 적이 나온다. 0.4.1 긴장감: 화면 가장자리가 붉게 맥박치고, HUD 에 WAVE n/m 과 제한 시간 바(스테이지 1은 20초, 2는 16초). 마지막 5초는 빨갛게 깜빡이며 째깍 소리, 시간이 다 되면 남은 적이 있어도 다음 웨이브가 증원으로 나온다 (마지막 웨이브는 제한 없음)</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>웨이브를 모두 잡으면 벽이 열리고 가운데에 보물상자가 떨어진다. 결투장 박쥐는 7~8행 (가운데 발판에 올라서면 맞는 높이). 제한 시간 안에 웨이브를 정리하면 남은 3초마다 코인 1 (FAST +n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>점프 버섯</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>바닥에 박힌 분홍 버섯. 밟고 지나가기만 해도 약 9칸 높이로 튀어 오르고 공중 점프·공중 대시가 다시 찬다.</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>절벽·가시밭을 넘거나 높은 길(숨은 상자)로 올라갈 때 쓴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>정예 적</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>금빛 기운과 체력 바, 체력 3배 (최소 +40). 스킬을 쓰기 전 머리 위에 빨간 "!" 로 0.5초 예고</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>경험치 4배, 코인 12, 하트 50%, 점수 500. 스킬(0.4.1): 슬라임 = 3초마다 플레이어 쪽으로 크게 뛰어들기, 쓰러지면 작은 슬라임 3 / 늑대 = 가까우면 빠르게 덮치기 / 마법사 = 부채꼴 3발 / 박쥐 = 3초마다 급강하 / 두꺼비 = 착지할 때 좌우 짧은 충격파</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>보물상자</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>아래 지면으로 떨어져 앉아 반짝인다. 닿으면 열린다.</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>코인 15 + 보너스 카드 1장 + 점수 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>깃발</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>기둥 위로 뛰어넘어도 클리어되도록 판정을 화면 위끝까지 넓힘</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>그림자 두꺼비 (0.4.1 새 적)</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>웅크렸다가 플레이어 쪽으로 크게 뛰어든다 (멀면 제자리에서 작게). 체력 26+10x스테이지, 경험치 3. 0.4.2: 뛰기 전에 떨어질 자리를 보고 구덩이면 덜 뛰거나 제자리에서 뛴다</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>스테이지 1·2 의 길과 결투장 웨이브에 섞여 나온다. 정예는 착지 충격파</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>스테이지</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>구간 (열)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>1 MISTY FIELDS (160칸)</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>0~25</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>슬라임 2, 첫 점프 버섯(6열) 위 발판의 코인, 구덩이</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr"/>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>26~55 결투장 1</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>W1 슬라임 3 / W2 늑대 2 + 발판 위 슬라임</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr"/>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>56~99</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>버섯으로 넘는 절벽(57열), 발판 위 마법사, 박쥐, 정예 늑대(81열), 버섯(86열) 위 높은 길의 숨은 상자(91열), 하트</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="38" t="inlineStr"/>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>100~129 결투장 2</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>W1 늑대 2 + 박쥐 2 / W2 마법사 2 + 슬라임 2 / W3 정예 늑대 + 슬라임 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr"/>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>130~159</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>슬라임, 박쥐, 계단, 깃발(155열)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>2 WHISPERING CAVE (180칸)</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>0~39</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>천장. 입구 적, 무너지는 다리, 버섯(28열)으로 넘는 가시밭</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr"/>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>40~69 결투장 1</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>W1 슬라임 3 + 박쥐 / W2 마법사 2 + 늑대 2 / W3 정예 마법사 + 박쥐 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr"/>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>70~113</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>무너지는 다리, 버섯(78열) + 가시밭, 정예 슬라임(89열), 버섯(95열) 위 천장 아래 숨은 상자(99열), 하트</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr"/>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>114~143 결투장 2</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="inlineStr">
+        <is>
+          <t>W1 늑대 3 / W2 마법사 2 + 박쥐 2 + 슬라임 / W3 정예 늑대 + 정예 마법사 + 박쥐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr"/>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>144~179</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>버섯(148열) + 가시밭, 적, 계단, 깃발(176열)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>검증 봇 (bot=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>목표 재탐색</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>30프레임마다 우선순위대로 목표를 다시 고른다: 결투장 적 &gt; 500px 안의 닫힌 보물상자 &gt; 지나쳐 버린 깃발 &gt; 전진</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>결투장</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>① 결투장 적만 목표 (같은 높이 우선) ② 위면 뛰어올라 발판, 아래면 발판 끝으로 내려감 ③ 120~260px 거리, 목표 쪽을 봄 ④ 계속 공격</t>
+        </is>
+      </c>
+      <c r="C26" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B24:C24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1022,7 +1476,7 @@
     <row r="2" ht="42" customHeight="1" s="37">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>보스 체력 300 고정. 체력 66% / 33% 아래로 내려가면 단계가 오르고(RAGE / FURY 배너) 카드를 1장씩 고른다. 단계마다 아래 목록에서 무작위로 고르며, 공격 사이 쉬는 시간은 60/48/36프레임. 수치는 "1단계 / 2단계 / 3단계" 순 (Source/Private/data/BossTuning.cpp). 60프레임 = 1초.</t>
+          <t>보스 체력 3000 고정 (0.4.2: 피해 10단위. 예전 단위 600 을 목표로, 공격력 3단계 빌드에서 같은 타수가 되게). 체력 66% / 33% 아래로 내려가면 단계가 오르고(RAGE / FURY 배너) 카드를 1장씩 고른다. 단계마다 아래 목록에서 무작위로 고르며, 공격 사이 쉬는 시간은 60/48/36프레임. 수치는 "1단계 / 2단계 / 3단계" 순 (Source/Private/data/BossTuning.cpp). 60프레임 = 1초.</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1674,12 @@
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>양쪽에서 박쥐 2마리를 부름 (이미 4마리 이상이면 생략)</t>
+          <t>양쪽에서 박쥐 2마리를 부름 (이미 4마리 이상이면 생략). 0.4.1: 박쥐가 순찰하지 않고 플레이어를 향해 천천히(1.7px/프레임) 날아옴</t>
         </is>
       </c>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>박쥐를 먼저 정리</t>
+          <t>박쥐를 먼저 정리. 다가오는 길목에 공을 깔아 둔다</t>
         </is>
       </c>
       <c r="J6" s="38" t="inlineStr">
@@ -2423,13 +2877,13 @@
         </is>
       </c>
       <c r="F4" s="19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>0.36</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.28</v>
       </c>
       <c r="I4" s="39" t="n">
         <v>-0.05</v>
@@ -2458,13 +2912,13 @@
         </is>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="I5" s="39" t="n">
         <v>0.02</v>
@@ -2493,13 +2947,13 @@
         </is>
       </c>
       <c r="F6" s="19" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="I6" s="39" t="n">
         <v>0.02</v>
@@ -2528,13 +2982,13 @@
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G7" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <v>0.08</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.1</v>
       </c>
       <c r="I7" s="39" t="n">
         <v>0.01</v>
@@ -2580,7 +3034,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>· 사용자 요청: 전설 확률을 스테이지 1/2/3에서 6% / 8% / 10%로. 나머지 등급도 같이 올려서 일반이 절반 아래가 되게 했다 (게임이 늘어지지 않도록).</t>
+          <t>· 0.4.5: 스테이지 1 일반 50% 기준으로 다시 맞춤. 일반 50/43/36%, 희귀 36/39/41%, 영웅 11/13/15%, 전설 3/5/8%</t>
         </is>
       </c>
     </row>
@@ -2630,7 +3084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6" customWidth="1" style="37" min="1" max="1"/>
@@ -2754,12 +3208,12 @@
       </c>
       <c r="G2" s="38" t="inlineStr">
         <is>
-          <t>섀도우볼 피해 증가 (공이 커지는 연출 유지)</t>
+          <t>섀도우볼 피해 증가 (공이 커지는 연출 유지). 0.4.2: 피해 10단위 (기본 10, 단계마다 +3, 최대 25)</t>
         </is>
       </c>
       <c r="H2" s="26" t="inlineStr">
         <is>
-          <t>피해 +1</t>
+          <t>피해 +3</t>
         </is>
       </c>
       <c r="I2" s="27" t="n">
@@ -2783,7 +3237,7 @@
       </c>
       <c r="N2" s="38" t="inlineStr">
         <is>
-          <t>기존 공격력 업그레이드(최대 4)를 5로. 밸런스: 너무 안 나와서 일반 -&gt; 희귀, 비중 4배. 0.3.1: 비중 4일 때 레벨업 화면 한 번에 나올 확률이 약 20%(희귀 칸의 4/19)라 너무 자주 보여서 비중 2로 (약 11%)</t>
+          <t>기존 공격력 업그레이드(최대 4)를 5로. 0.4.2: 한 장에 피해가 두 배가 되던 1 단위를 10 단위로 바꾸고, 뽑힐 비중도 같은 등급 카드와 같게(1) — 비중 4·2 모두 너무 자주 나왔다</t>
         </is>
       </c>
     </row>
@@ -2909,7 +3363,11 @@
           <t>하</t>
         </is>
       </c>
-      <c r="N4" s="38" t="n"/>
+      <c r="N4" s="38" t="inlineStr">
+        <is>
+          <t>0.4.7: 실제 사거리 = 속도 x 수명(기본 36 + 공격력 단계마다 3, 사거리 +20%/단계) x 튕김 1.6 x 산탄 0.55 x 레이저 2.6배 속도. 능력치 패널 RANGE 가 이 값</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -3383,7 +3841,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>영웅</t>
+          <t>희귀</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -3427,7 +3885,7 @@
       </c>
       <c r="N12" s="38" t="inlineStr">
         <is>
-          <t>타일 충돌 시 반사, 뜬 발판은 통과. 0.2.3 재설계: 벽에서만 튕겨서 쓸모가 적었음 → 적에게도 튕김. 3/5번일 때 보스 피해가 약 4배여서 2/3번으로 조정</t>
+          <t>타일 충돌 시 반사, 뜬 발판은 통과. 0.2.3 재설계: 벽에서만 튕겨서 쓸모가 적었음 → 적에게도 튕김. 3/5번일 때 보스 피해가 약 4배여서 2/3번으로 조정 / 0.4.2: 영웅 -&gt; 희귀</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3973,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>영웅</t>
+          <t>희귀</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3559,7 +4017,7 @@
       </c>
       <c r="N14" s="38" t="inlineStr">
         <is>
-          <t>밸런스: +25% 는 기본 피해 1에서 반올림되어 효과가 없었음 -&gt; 2초간 2배. 보스에게 2배가 계속 이어지지 않도록 대상별 15초 쿨타임</t>
+          <t>밸런스: +25% 는 기본 피해 1에서 반올림되어 효과가 없었음 -&gt; 2초간 2배. 보스에게 2배가 계속 이어지지 않도록 대상별 15초 쿨타임 / 0.4.2: 영웅 -&gt; 희귀</t>
         </is>
       </c>
     </row>
@@ -3581,7 +4039,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>전설</t>
+          <t>영웅</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -3596,12 +4054,12 @@
       </c>
       <c r="G15" s="38" t="inlineStr">
         <is>
-          <t>섀도우볼이 가장 가까운 적을 향해 휘어서 날아감. 대신 공격력 -1 (최소 1)</t>
+          <t>섀도우볼이 가장 가까운 적을 향해 휘어서 날아감. 대신 피해 -3 (최소 7)</t>
         </is>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>유도 / 공격력 -1</t>
+          <t>유도 / 피해 -3</t>
         </is>
       </c>
       <c r="I15" s="27" t="n">
@@ -3625,7 +4083,7 @@
       </c>
       <c r="N15" s="38" t="inlineStr">
         <is>
-          <t>사용자: 전설 카드. 밸런스: 맞히기 쉬운 대신 공격력 -1 (최소 1)</t>
+          <t>사용자: 전설 카드였으나 0.4.2 새 카드(혈사포 등)가 늘어 영웅으로. 맞히기 쉬운 대신 피해 -3</t>
         </is>
       </c>
     </row>
@@ -3713,7 +4171,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>전설</t>
+          <t>영웅</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -3757,7 +4215,7 @@
       </c>
       <c r="N17" s="38" t="inlineStr">
         <is>
-          <t>누르고 있는 동안 연사는 멈춤. 단계마다 빛 색(보라→하늘→분홍→금)과 머리 위 점으로 표시. 0.2.3: 1초 3배 고정은 보스전에서 손해라 단계식으로</t>
+          <t>누르고 있는 동안 연사는 멈춤. 단계마다 빛 색(보라→하늘→분홍→금)과 머리 위 점으로 표시. 0.2.3: 1초 3배 고정은 보스전에서 손해라 단계식으로 / 0.4.2: 멀티샷이 있으면 차지 공도 같은 수만큼 부채꼴로. 혈사포와 함께 나오지 않음. 전설 -&gt; 영웅</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4508,12 @@
       </c>
       <c r="G22" s="38" t="inlineStr">
         <is>
-          <t>몸통으로 부딪힌 적에게 피해 3</t>
+          <t>부딪힌 적에게 피해 30</t>
         </is>
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>반격 3</t>
+          <t>반격 30</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
@@ -4339,12 +4797,12 @@
       </c>
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>다단 점프</t>
+          <t>더블 점프</t>
         </is>
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>AIR JUMP</t>
+          <t>DOUBLE JUMP</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -4393,7 +4851,7 @@
       </c>
       <c r="N27" s="38" t="inlineStr">
         <is>
-          <t>기존 이단 점프(최대 1)를 2로</t>
+          <t>기존 이단 점프(최대 1)를 2로 0.4.2: 등 뒤에 작은 박쥐 날개 (단계마다 한 쌍) / 0.4.7: 게임 표기 AIR JUMP -&gt; DOUBLE JUMP (더블 점프 카드가 없는 줄 알아서)</t>
         </is>
       </c>
     </row>
@@ -4624,7 +5082,7 @@
       </c>
       <c r="G31" s="38" t="inlineStr">
         <is>
-          <t>대시 칸 +1 (연속으로 대시 가능, HUD에 칸 표시)</t>
+          <t>대시 칸 +1 (연속으로 대시 가능, HUD에 칸 표시). 공중 대시 횟수도 +1</t>
         </is>
       </c>
       <c r="H31" s="26" t="inlineStr">
@@ -4653,7 +5111,7 @@
       </c>
       <c r="N31" s="38" t="inlineStr">
         <is>
-          <t>사용자: 대시 가능 칸 + 횟수 증가. 기본 1칸 → 최대 3칸. 중첩 가능한 특수 능력</t>
+          <t>사용자: 대시 가능 칸 + 횟수 증가. 기본 1칸 → 최대 3칸. 중첩 가능한 특수 능력 / 0.4.3: 공중에서는 연속 대시가 안 되던 문제 -&gt; 공중 대시 횟수 = 1 + 공중 대시 + 대시 칸</t>
         </is>
       </c>
     </row>
@@ -5857,21 +6315,21 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>특수</t>
+          <t>특수(중첩)</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
         <is>
-          <t>작은 겐가 분신이 따라다니며 0.8초마다 가장 가까운 적에게 자동 사격 (내 공의 특수 능력도 같이 적용)</t>
+          <t>작은 겐가 분신이 플레이어 뒤로 한 줄로 따라다니며 0.8초마다 플레이어와 같은 공격(같은 발 수, 같은 공 능력, 크기 70%·피해 50%)을 가장 가까운 적에게 쏜다. 최대 3마리</t>
         </is>
       </c>
       <c r="H50" s="26" t="inlineStr">
         <is>
-          <t>분신 1</t>
+          <t>분신 +1</t>
         </is>
       </c>
       <c r="I50" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50" s="38" t="n"/>
       <c r="K50" s="38" t="inlineStr">
@@ -5891,13 +6349,739 @@
       </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
-          <t>도트 스프라이트 1종 추가 필요. 0.3.1: 스테이지 중에 얻으면 다음 스테이지가 아니라 바로 나오도록 수정</t>
+          <t>0.4.6: 내 사격에 맞춰 쏘던 것(0.4.2)을 다시 0.8초 주기로. 여러 마리면 쏘는 때를 0.27초씩 엇갈림. 0.4.3: 최대 3마리</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1" s="37">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B51" s="38" t="inlineStr">
+        <is>
+          <t>혈사포</t>
+        </is>
+      </c>
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>BRIMSTONE</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G51" s="38" t="inlineStr">
+        <is>
+          <t>보통 공 대신 Z 를 0.75초 모았다가 떼면 화면 끝까지 굵은 핏빛 광선 0.5초. 모든 적 관통, 3프레임마다 공격력 x0.6 (약 6배)</t>
+        </is>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>광선</t>
+        </is>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>차지샷·레이저 없음</t>
+        </is>
+      </c>
+      <c r="K51" s="38" t="inlineStr">
+        <is>
+          <t>핏빛 광선 + 뿔</t>
+        </is>
+      </c>
+      <c r="L51" s="38" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="N51" s="38" t="inlineStr">
+        <is>
+          <t>아이작의 혈사포. 멀티샷 1발마다 광선 10px 굵게. 얻으면 머리에 빨간 뿔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="27" customHeight="1" s="37">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="B52" s="38" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="C52" s="38" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G52" s="38" t="inlineStr">
+        <is>
+          <t>공이 2.6배 빠른 가는 레이저가 되어 모든 적을 관통. 피해 70%</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="38" t="inlineStr">
+        <is>
+          <t>혈사포 없음</t>
+        </is>
+      </c>
+      <c r="K52" s="38" t="inlineStr">
+        <is>
+          <t>분홍 빛줄기</t>
+        </is>
+      </c>
+      <c r="L52" s="38" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N52" s="38" t="inlineStr">
+        <is>
+          <t>공 모양 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="27" customHeight="1" s="37">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="B53" s="38" t="inlineStr">
+        <is>
+          <t>부메랑</t>
+        </is>
+      </c>
+      <c r="C53" s="38" t="inlineStr">
+        <is>
+          <t>BOOMERANG</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G53" s="38" t="inlineStr">
+        <is>
+          <t>사거리 절반에서 돌아서 플레이어에게 돌아오며 다시 맞힘</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>되돌아옴</t>
+        </is>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="38" t="inlineStr">
+        <is>
+          <t>휘어진 화살표</t>
+        </is>
+      </c>
+      <c r="L53" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N53" s="38" t="inlineStr">
+        <is>
+          <t>공 모양 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="27" customHeight="1" s="37">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="B54" s="38" t="inlineStr">
+        <is>
+          <t>웨이브</t>
+        </is>
+      </c>
+      <c r="C54" s="38" t="inlineStr">
+        <is>
+          <t>WAVE SHOT</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G54" s="38" t="inlineStr">
+        <is>
+          <t>공이 진행 방향 옆으로 사인파(진폭 16px)처럼 출렁임. 처음에는 위로 출렁이고, 벽·바닥 충돌은 출렁임을 뺀 중심선으로 판단</t>
+        </is>
+      </c>
+      <c r="H54" s="26" t="inlineStr">
+        <is>
+          <t>출렁임</t>
+        </is>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="38" t="inlineStr">
+        <is>
+          <t>물결</t>
+        </is>
+      </c>
+      <c r="L54" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="N54" s="38" t="inlineStr">
+        <is>
+          <t>공 모양 변경. 0.4.5: 바닥 가까이서 쏘면 출렁임 때문에 바로 땅에 닿아 사라지던 문제 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1" s="37">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="B55" s="38" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="C55" s="38" t="inlineStr">
+        <is>
+          <t>SCATTER</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G55" s="38" t="inlineStr">
+        <is>
+          <t>공 +2발을 넓은 부채꼴로. 사거리 55%, 한 발 피해 80%</t>
+        </is>
+      </c>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>+2발</t>
+        </is>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="38" t="inlineStr">
+        <is>
+          <t>퍼지는 점</t>
+        </is>
+      </c>
+      <c r="L55" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="N55" s="38" t="inlineStr">
+        <is>
+          <t>근접 메타</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1" s="37">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="B56" s="38" t="inlineStr">
+        <is>
+          <t>무거운 공</t>
+        </is>
+      </c>
+      <c r="C56" s="38" t="inlineStr">
+        <is>
+          <t>HEAVY SHOT</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G56" s="38" t="inlineStr">
+        <is>
+          <t>공 크기 1.45배, 피해 +40%, 연사 25% 느림</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>크고 느림</t>
+        </is>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="38" t="n"/>
+      <c r="K56" s="38" t="inlineStr">
+        <is>
+          <t>큰 공</t>
+        </is>
+      </c>
+      <c r="L56" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="N56" s="38" t="n"/>
+    </row>
+    <row r="57" ht="27" customHeight="1" s="37">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="B57" s="38" t="inlineStr">
+        <is>
+          <t>독</t>
+        </is>
+      </c>
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>POISON</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G57" s="38" t="inlineStr">
+        <is>
+          <t>맞은 적이 3초 동안 0.5초마다 그 피해의 25% (약 1.5배 더). 보스도 걸림</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>지속 피해</t>
+        </is>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="38" t="n"/>
+      <c r="K57" s="38" t="inlineStr">
+        <is>
+          <t>초록 방울</t>
+        </is>
+      </c>
+      <c r="L57" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N57" s="38" t="inlineStr">
+        <is>
+          <t>머리 위 초록 방울 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="27" customHeight="1" s="37">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="B58" s="38" t="inlineStr">
+        <is>
+          <t>냉기</t>
+        </is>
+      </c>
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>FROST</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G58" s="38" t="inlineStr">
+        <is>
+          <t>맞은 적이 2초 동안 이동 속도 절반. 보스는 느려지지 않음</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>느려짐</t>
+        </is>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="38" t="n"/>
+      <c r="K58" s="38" t="inlineStr">
+        <is>
+          <t>눈송이</t>
+        </is>
+      </c>
+      <c r="L58" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N58" s="38" t="inlineStr">
+        <is>
+          <t>머리 위 눈송이 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="27" customHeight="1" s="37">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B59" s="38" t="inlineStr">
+        <is>
+          <t>연쇄 번개</t>
+        </is>
+      </c>
+      <c r="C59" s="38" t="inlineStr">
+        <is>
+          <t>CHAIN BOLT</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G59" s="38" t="inlineStr">
+        <is>
+          <t>맞힐 때마다 170px 안의 가장 가까운 다른 적에게 번개 50%</t>
+        </is>
+      </c>
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>연쇄 1</t>
+        </is>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="38" t="n"/>
+      <c r="K59" s="38" t="inlineStr">
+        <is>
+          <t>번개</t>
+        </is>
+      </c>
+      <c r="L59" s="38" t="inlineStr">
+        <is>
+          <t>기획 추가</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N59" s="38" t="n"/>
+    </row>
+    <row r="60" ht="27" customHeight="1" s="37">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B60" s="38" t="inlineStr">
+        <is>
+          <t>그림자 궤도</t>
+        </is>
+      </c>
+      <c r="C60" s="38" t="inlineStr">
+        <is>
+          <t>SHADOW ORBIT</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>특수(중첩)</t>
+        </is>
+      </c>
+      <c r="G60" s="38" t="inlineStr">
+        <is>
+          <t>몸 주위를 도는 구슬 2개(2단계 4개). 닿은 적에게 공격력 x0.6, 적 탄환을 막음</t>
+        </is>
+      </c>
+      <c r="H60" s="26" t="inlineStr">
+        <is>
+          <t>구슬 +2</t>
+        </is>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" s="38" t="n"/>
+      <c r="K60" s="38" t="inlineStr">
+        <is>
+          <t>도는 구슬</t>
+        </is>
+      </c>
+      <c r="L60" s="38" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N60" s="38" t="inlineStr">
+        <is>
+          <t>따라다니는 친구처럼 겉모습이 바뀌는 카드</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>그림자 날개</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>SHADOW WINGS</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
+      </c>
+      <c r="G61" s="38" t="inlineStr">
+        <is>
+          <t>등 뒤에 큰 날개가 돋고, 공중에서 점프를 누르고 있으면 위로 난다. 비행 2.5초(몸 아래 바), 땅에 있으면 다시 참. 다 쓰면 천천히 활공</t>
+        </is>
+      </c>
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>비행 2.5초</t>
+        </is>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="38" t="n"/>
+      <c r="K61" s="38" t="inlineStr">
+        <is>
+          <t>큰 박쥐 날개</t>
+        </is>
+      </c>
+      <c r="L61" s="38" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="M61" s="10" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="N61" s="38" t="inlineStr">
+        <is>
+          <t>0.4.7 추가. 화면 맨 위 근처로는 못 올라감. 겉모습이 바뀌는 카드</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N50"/>
-  <conditionalFormatting sqref="D2:D50">
+  <autoFilter ref="A1:N61"/>
+  <conditionalFormatting sqref="D2:D60">
     <cfRule type="expression" priority="1" dxfId="7">
       <formula>$D2="일반"</formula>
     </cfRule>
@@ -5911,7 +7095,7 @@
       <formula>$D2="전설"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F50">
+  <conditionalFormatting sqref="F2:F60">
     <cfRule type="expression" priority="5" dxfId="3">
       <formula>$F2="능력치"</formula>
     </cfRule>
@@ -5950,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30" customWidth="1" style="37" min="1" max="1"/>
@@ -6326,6 +7510,125 @@
       <c r="C25" s="38" t="inlineStr">
         <is>
           <t>공 하나당 분열 1번 (적이든 벽이든 먼저 닿은 곳)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>혈사포 + 차지샷 / 레이저</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>함께 나오지 않음 (혈사포가 있으면 둘은 제시 목록에서 빠지고, 반대도 같다)</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>혈사포 + 멀티샷</t>
+        </is>
+      </c>
+      <c r="B27" s="38" t="inlineStr">
+        <is>
+          <t>광선이 1발마다 10px 굵어짐</t>
+        </is>
+      </c>
+      <c r="C27" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>혈사포 + 저주/독/냉기/치명타</t>
+        </is>
+      </c>
+      <c r="B28" s="38" t="inlineStr">
+        <is>
+          <t>광선 한 번 한 번에 모두 적용</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>차지샷 + 멀티샷 (0.4.2)</t>
+        </is>
+      </c>
+      <c r="B29" s="38" t="inlineStr">
+        <is>
+          <t>차지 공도 멀티샷 수만큼 부채꼴로</t>
+        </is>
+      </c>
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>산탄 + 멀티샷</t>
+        </is>
+      </c>
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>발 수가 더해짐 (예: 멀티샷 2 + 산탄 = 5발)</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>분신 + 모든 사격</t>
+        </is>
+      </c>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>0.8초마다 내 공격과 같은 발 수, 같은 공 능력 (피해 50%)</t>
+        </is>
+      </c>
+      <c r="C31" s="38" t="inlineStr">
+        <is>
+          <t>쏠 적이 없으면 쏘지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>부메랑 + 관통/튕김</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>돌아오는 길에 이미 맞힌 적도 다시 맞힘</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6431,14 +7734,14 @@
       </c>
       <c r="E4" s="38" t="inlineStr">
         <is>
-          <t>화면 전체에 충격파 한 번. 화면 안의 적 전부에게 피해 (지금 필살기 그대로)</t>
+          <t>화면 전체에 충격파 한 번. 화면 안의 적 전부에게 피해. 0.4.3: 광역이라 너프 (일반 35 + 공격력 단계마다 3, 보스 120). 피해 10단위</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0</v>
@@ -7199,7 +8502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="37" min="1" max="1"/>
@@ -7226,7 +8529,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>확정: 1회 50코인 고정. 오르는 가격은 0 (나중에 바꾸고 싶으면 B4만 고치면 된다)</t>
+          <t>0.4.6: 첫 뽑기 50코인, 그 판에서 뽑을 때마다 +25, 상한 없음. 다음 상점에도 이어진다 (스테이지 1 뒤 상점에서 75까지 뽑았으면 스테이지 2 뒤 상점은 100부터)</t>
         </is>
       </c>
     </row>
@@ -7237,7 +8540,7 @@
         </is>
       </c>
       <c r="B4" s="33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -7248,7 +8551,7 @@
       </c>
       <c r="B5" s="33" t="inlineStr">
         <is>
-          <t>50코인 고정 (확정)</t>
+          <t>50 + 25 x (이번 판에서 상점에서 뽑은 횟수)</t>
         </is>
       </c>
     </row>
@@ -7675,21 +8978,104 @@
       <c r="G34" s="41" t="n"/>
       <c r="H34" s="42" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>카드 강화 (0.4.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="38" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B37" s="38" t="inlineStr">
+        <is>
+          <t>오른쪽 가운데 칸 (뽑기 아래, 다음 스테이지 위). 예전 안내 글 자리에 만들고 출발 칸과 자리를 바꿈</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="n"/>
+      <c r="D37" s="41" t="n"/>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="41" t="n"/>
+      <c r="G37" s="41" t="n"/>
+      <c r="H37" s="42" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>얻은 카드 중 같은 카드를 또 얻으면 단계가 오르는 것(능력치, 특수(중첩))이고 아직 최대 단계가 아닌 것</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="42" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>등급 기본값 + 지금 단계 x 20. 기본값: 일반 60 / 희귀 90 / 영웅 140 / 전설 200 (뽑기 첫 가격 50 보다 비싸게)</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="41" t="n"/>
+      <c r="H39" s="42" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+      <c r="B40" s="38" t="inlineStr">
+        <is>
+          <t>0.4.5 목록형으로 다시: 강화 칸에서 Z -&gt; 올릴 수 있는 카드가 한 줄씩(아이콘, 이름, 등급, 단계 칸에서 오를 칸은 금색, LV 2 &gt; 3, 가격). ↑ ↓ 로 고르고 Z 로 올림, Esc 로 돌아감. 위에 가진 코인과 "무엇을 하는 화면인지" 설명, 아래에 고른 카드의 자세한 설명과 "Z 를 누르면 몇 코인" 안내. 코인이 모자라면 가격과 안내가 빨갛다</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="41" t="n"/>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="42" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B34:H34"/>
     <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
